--- a/data/trans_dic/P16A04-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A04-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,38</t>
+          <t>2,18; 4,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,81</t>
+          <t>2,3; 4,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,12</t>
+          <t>0,66; 2,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,79</t>
+          <t>2,51; 6,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,43</t>
+          <t>1,7; 3,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,66</t>
+          <t>1,86; 3,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,47</t>
+          <t>1,46; 3,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,87; 7,69</t>
+          <t>3,94; 7,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,6</t>
+          <t>2,21; 3,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,8</t>
+          <t>2,27; 3,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,58</t>
+          <t>1,25; 2,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 6,42</t>
+          <t>3,66; 6,6</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,86</t>
+          <t>0,82; 1,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,67</t>
+          <t>2,03; 3,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,94</t>
+          <t>1,57; 2,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,92</t>
+          <t>1,32; 2,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,11</t>
+          <t>1,54; 3,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,26</t>
+          <t>2,53; 4,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,71</t>
+          <t>1,51; 2,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,24</t>
+          <t>1,69; 3,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,24</t>
+          <t>1,34; 2,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 3,69</t>
+          <t>2,52; 3,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,63</t>
+          <t>1,74; 2,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,81</t>
+          <t>1,75; 2,81</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,1</t>
+          <t>0,19; 1,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,72</t>
+          <t>0,69; 3,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,41</t>
+          <t>1,41; 4,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,28</t>
+          <t>0,55; 2,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,51</t>
+          <t>0,45; 2,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,47</t>
+          <t>0,65; 3,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,51</t>
+          <t>1,44; 4,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,51</t>
+          <t>1,39; 3,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,87</t>
+          <t>0,49; 1,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,87</t>
+          <t>0,92; 2,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,75</t>
+          <t>1,68; 3,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,52</t>
+          <t>1,2; 2,61</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,28</t>
+          <t>1,38; 2,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,5</t>
+          <t>2,26; 3,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,55</t>
+          <t>1,58; 2,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,8</t>
+          <t>1,58; 2,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,77</t>
+          <t>1,75; 2,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 3,5</t>
+          <t>2,26; 3,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,75</t>
+          <t>1,73; 2,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 3,65</t>
+          <t>2,48; 3,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,38</t>
+          <t>1,69; 2,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,3</t>
+          <t>2,45; 3,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,54</t>
+          <t>1,79; 2,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,11</t>
+          <t>2,15; 3,08</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22977; 45223</t>
+          <t>22476; 46337</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21300; 46676</t>
+          <t>22349; 47366</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4851; 15971</t>
+          <t>5001; 16514</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12721; 29747</t>
+          <t>12909; 30851</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22536; 45086</t>
+          <t>22397; 45345</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24489; 48855</t>
+          <t>24843; 48500</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14638; 34511</t>
+          <t>14570; 34833</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29076; 57834</t>
+          <t>29632; 58043</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51906; 84507</t>
+          <t>51894; 83695</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52302; 87502</t>
+          <t>52353; 85416</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21008; 45180</t>
+          <t>21831; 43903</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>46483; 81272</t>
+          <t>46290; 83459</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13275; 31424</t>
+          <t>13794; 32702</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40174; 71975</t>
+          <t>39853; 72925</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33468; 61039</t>
+          <t>32603; 59975</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31184; 66811</t>
+          <t>30237; 66649</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23570; 49429</t>
+          <t>24428; 48614</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42847; 74624</t>
+          <t>44333; 76972</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29614; 53814</t>
+          <t>30122; 55532</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40143; 72477</t>
+          <t>37814; 70243</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43732; 73466</t>
+          <t>44104; 74700</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91974; 136887</t>
+          <t>93358; 138249</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68874; 106964</t>
+          <t>70530; 108108</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>79934; 127016</t>
+          <t>79237; 127188</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1514; 11587</t>
+          <t>1073; 10604</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3128; 17880</t>
+          <t>3330; 17526</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7427; 24101</t>
+          <t>7688; 24166</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3656; 14775</t>
+          <t>3562; 14926</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2642; 11978</t>
+          <t>2136; 11512</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2718; 15879</t>
+          <t>2990; 13996</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7379; 24768</t>
+          <t>7911; 23980</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9475; 23161</t>
+          <t>9191; 22310</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5005; 19246</t>
+          <t>5006; 18574</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8489; 26885</t>
+          <t>8589; 27437</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18909; 41124</t>
+          <t>18447; 41504</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15541; 32971</t>
+          <t>15678; 34118</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45782; 74568</t>
+          <t>45311; 75059</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>77738; 119220</t>
+          <t>77113; 119499</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53573; 86115</t>
+          <t>53235; 86888</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56888; 96559</t>
+          <t>54648; 95804</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58066; 93580</t>
+          <t>59272; 93543</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>82406; 123886</t>
+          <t>79906; 124321</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61414; 97199</t>
+          <t>61160; 97641</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>87593; 133162</t>
+          <t>90587; 136173</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>112047; 158487</t>
+          <t>112191; 155307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>170160; 229323</t>
+          <t>170256; 231256</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>123331; 175181</t>
+          <t>123705; 174955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>156341; 220626</t>
+          <t>152992; 218504</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A04-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A04-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,49</t>
+          <t>2,17; 4,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,88</t>
+          <t>2,32; 4,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,19</t>
+          <t>0,61; 2,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,01</t>
+          <t>2,45; 5,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,45</t>
+          <t>1,81; 3,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,64</t>
+          <t>1,88; 3,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,5</t>
+          <t>1,44; 3,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,72</t>
+          <t>3,69; 6,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,57</t>
+          <t>2,19; 3,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,71</t>
+          <t>2,28; 3,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,51</t>
+          <t>1,25; 2,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,6</t>
+          <t>3,54; 5,52</t>
         </is>
       </c>
     </row>
@@ -804,27 +804,27 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>2,07%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,93</t>
+          <t>0,83; 1,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,72</t>
+          <t>2,08; 3,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,89</t>
+          <t>1,56; 2,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,91</t>
+          <t>1,77; 3,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,06</t>
+          <t>1,57; 3,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,4</t>
+          <t>2,56; 4,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,79</t>
+          <t>1,5; 2,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,14</t>
+          <t>2,3; 3,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,28</t>
+          <t>1,33; 2,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,73</t>
+          <t>2,49; 3,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,66</t>
+          <t>1,7; 2,65</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,81</t>
+          <t>2,18; 3,12</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,92</t>
+          <t>0,27; 2,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,65</t>
+          <t>0,83; 4,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,42</t>
+          <t>1,45; 4,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,31</t>
+          <t>0,52; 1,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,42</t>
+          <t>0,56; 2,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,06</t>
+          <t>0,61; 3,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,37</t>
+          <t>1,48; 4,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,38</t>
+          <t>1,78; 4,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,81</t>
+          <t>0,49; 1,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,93</t>
+          <t>0,85; 2,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,79</t>
+          <t>1,73; 3,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,61</t>
+          <t>1,37; 2,75</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,29</t>
+          <t>1,4; 2,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,51</t>
+          <t>2,28; 3,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,57</t>
+          <t>1,58; 2,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,78</t>
+          <t>1,82; 2,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,77</t>
+          <t>1,7; 2,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,51</t>
+          <t>2,33; 3,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,76</t>
+          <t>1,76; 2,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 3,73</t>
+          <t>2,8; 3,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,33</t>
+          <t>1,69; 2,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,33</t>
+          <t>2,48; 3,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,53</t>
+          <t>1,81; 2,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,08</t>
+          <t>2,49; 3,25</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>21842</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39714</t>
+          <t>39776</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59855</t>
+          <t>61617</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22476; 46337</t>
+          <t>22368; 43991</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22349; 47366</t>
+          <t>22462; 46282</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5001; 16514</t>
+          <t>4623; 16494</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12909; 30851</t>
+          <t>14119; 31414</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22397; 45345</t>
+          <t>23809; 47002</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24843; 48500</t>
+          <t>25047; 49772</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14570; 34833</t>
+          <t>14330; 34313</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29632; 58043</t>
+          <t>30231; 50682</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51894; 83695</t>
+          <t>51452; 84468</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52353; 85416</t>
+          <t>52526; 87248</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21831; 43903</t>
+          <t>21817; 45194</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>46290; 83459</t>
+          <t>49487; 77108</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47320</t>
+          <t>52621</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>55644</t>
+          <t>62950</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>102964</t>
+          <t>115571</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13794; 32702</t>
+          <t>13974; 31745</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39853; 72925</t>
+          <t>40802; 74599</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32603; 59975</t>
+          <t>32392; 61179</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30237; 66649</t>
+          <t>39529; 72230</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24428; 48614</t>
+          <t>24976; 48369</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44333; 76972</t>
+          <t>44742; 79002</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30122; 55532</t>
+          <t>29800; 55816</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37814; 70243</t>
+          <t>50028; 77193</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44104; 74700</t>
+          <t>43678; 74533</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93358; 138249</t>
+          <t>92264; 138025</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70530; 108108</t>
+          <t>68925; 107598</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>79237; 127188</t>
+          <t>96060; 137194</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15206</t>
+          <t>20209</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22940</t>
+          <t>27894</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1073; 10604</t>
+          <t>1475; 11113</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3330; 17526</t>
+          <t>3973; 19833</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7688; 24166</t>
+          <t>7926; 24440</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3562; 14926</t>
+          <t>3727; 14038</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2136; 11512</t>
+          <t>2658; 12100</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2990; 13996</t>
+          <t>2781; 14789</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7911; 23980</t>
+          <t>8127; 25250</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9191; 22310</t>
+          <t>13091; 31046</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5006; 18574</t>
+          <t>5020; 17835</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8589; 27437</t>
+          <t>7993; 27875</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18447; 41504</t>
+          <t>18956; 41120</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15678; 34118</t>
+          <t>19846; 39784</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75194</t>
+          <t>82148</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>110564</t>
+          <t>122935</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>185759</t>
+          <t>205082</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45311; 75059</t>
+          <t>45808; 76703</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>77113; 119499</t>
+          <t>77692; 120791</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53235; 86888</t>
+          <t>53475; 88669</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54648; 95804</t>
+          <t>64166; 103773</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>59272; 93543</t>
+          <t>57529; 93713</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79906; 124321</t>
+          <t>82634; 125505</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61160; 97641</t>
+          <t>62231; 99772</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>90587; 136173</t>
+          <t>104303; 143613</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>112191; 155307</t>
+          <t>112708; 159284</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>170256; 231256</t>
+          <t>172046; 229515</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>123705; 174955</t>
+          <t>125116; 172196</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>152992; 218504</t>
+          <t>180038; 235642</t>
         </is>
       </c>
     </row>
